--- a/assets/aGTM-Events-v1.4.xlsx
+++ b/assets/aGTM-Events-v1.4.xlsx
@@ -4399,7 +4399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4529,82 +4529,94 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Only one variable template</t>
+          <t>Which v1.4 exactly</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>v1.4.1 ships only aGTM var - Content Counter. The Consent-Check and Consent-Info variables were added afterwards (CHANGELOG entry 1.4.2, never tagged/released) and ship with v1.5.</t>
+          <t>This sheet describes v1.4.1, the last TAGGED release. Two later states shipped unofficially without a tag: 1.4.2 (aGTM.js carries @version 1.4.2 from 2025-09-09 until the v1.5 bump) and 1.4.3pre, which git does not record as a version at all. The events and attributes below apply to all three - they differ in CMP adapters, variable templates and build tooling, not in events.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>No per-event flags</t>
+          <t>Variable templates differ</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>The flags _noConsent, _noDLPush and _post (POST transport) are v1.5 only. In v1.4.x every non-aGTM* event is consent-gated, without exception.</t>
+          <t>v1.4.1 ships only aGTM var - Content Counter; aGTM var - Consent Check and aGTM var - Consent Info came with the unofficial 1.4.2. Whether you have them depends on which of the three states you run.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>aGTM_consent_update is not gated</t>
+          <t>No per-event flags</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>In v1.4.x the event fires on every run_cc('update') run. v1.5 only fires it on a changed consent state (hash gating).</t>
+          <t>The flags _noConsent, _noDLPush and _post (POST transport) are v1.5 only. In v1.4.x every non-aGTM* event is consent-gated, without exception.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>No session/attribution/bot data</t>
+          <t>aGTM_consent_update is not gated</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>aGTM.d.session, aGTM.d.attribution and aGTM.d.bot come with the v1.5 sGTM Client. In v1.4.x only aGTM.d.consent, aGTM.d.dl and aGTM.l exist.</t>
+          <t>In v1.4.x the event fires on every run_cc('update') run. v1.5 only fires it on a changed consent state (hash gating).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
+          <t>No session/attribution/bot data</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>aGTM.d.session, aGTM.d.attribution and aGTM.d.bot come with the v1.5 sGTM Client. In v1.4.x only aGTM.d.consent, aGTM.d.dl and aGTM.l exist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
           <t>DL-Repeat is tag-only</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>The replay engine (gate wait, poll, late enrichment, aGTM_repeat_fallback) moved into the library with v1.5. The v1.4.x tag only marks replayed events with aGTMrepeated = true.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>aGTM version</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>v1.4  (DEPRECATED)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
+          <t>aGTM version</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>v1.4  (DEPRECATED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Generated from the aGTM sources (aGTM.js + gtm/**/*.tpl). Companion to EVENTS-v1.4.md in the repository, which additionally covers the consent gate, the event flags and the aGTM.* JavaScript paths.</t>
         </is>

--- a/assets/aGTM-Events-v1.4.xlsx
+++ b/assets/aGTM-Events-v1.4.xlsx
@@ -4534,7 +4534,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>This sheet describes v1.4.1, the last TAGGED release. Two later states shipped unofficially without a tag: 1.4.2 (aGTM.js carries @version 1.4.2 from 2025-09-09 until the v1.5 bump) and 1.4.3pre, which git does not record as a version at all. The events and attributes below apply to all three - they differ in CMP adapters, variable templates and build tooling, not in events.</t>
+          <t>This sheet describes v1.4.1, the last TAGGED release. Two later states shipped unofficially without a tag: 1.4.2 (aGTM.js carries @version 1.4.2 from 2025-09-09 until the v1.5 bump) and 1.4.3pre, which is a sGTM CLIENT version, not a library one - the library embedded in that client still reports 1.4.2. The events and attributes below apply to all three - they differ in CMP adapters, variable templates, build tooling and server-side client behaviour, not in events.</t>
         </is>
       </c>
     </row>
